--- a/tests/fixtures/synthetic_certificados.xlsx
+++ b/tests/fixtures/synthetic_certificados.xlsx
@@ -530,8 +530,10 @@
       <c r="J2" t="n">
         <v>2026</v>
       </c>
-      <c r="K2" t="n">
-        <v>1</v>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-1</t>
+        </is>
       </c>
       <c r="L2" t="n">
         <v>1</v>
